--- a/Haplotypes_identification_key.xlsx
+++ b/Haplotypes_identification_key.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\FSHD\DUCKS4_2.1_GITHUB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\GITHUB\v1.1.0\ducks4_wovar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55455FAE-C00F-4A70-8013-ABCFDAC30A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7090A551-8898-4284-A1C6-A5A9515BFB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HP-identifiction-KEY" sheetId="16" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="HP_regions" sheetId="13" r:id="rId4"/>
     <sheet name="AS_regions" sheetId="14" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -2114,6 +2117,89 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2126,120 +2212,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2248,20 +2235,36 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2382,8 +2385,8 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>2028824</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2399,7 +2402,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="771524" y="942975"/>
-          <a:ext cx="11182350" cy="2038350"/>
+          <a:ext cx="11182350" cy="2152650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2441,8 +2444,31 @@
         <a:p>
           <a:r>
             <a:rPr lang="de-AT" sz="1100"/>
-            <a:t>The table is to be read from left to right: the first 6 columns (title DUCKS4) are the results from the DUCKS4 detailed output for the haplotypes and the composition of the repeat-sequence. The columns 7 to 9 (title Haplotype results) shows the resulting haplotype, permissive haplotypes are marked red. The columns 10-11 (title manual check) are displaying the data relevant for the manual check. Relevant is the SSLP repeat in CLUHP-4-201 gene (SSLP: chr4:193430066-193430226, T2T-chm13v2.0) and the first 3-5 repeat units with the restriction enzyme sites of the D4Z4-array for manual inspection within the alignment bam-files of the haplotypes from the DUCKS4-output. With the restriction enzyme sites (BinI (B)/XapI (X)) from Southern Blotting three types of RU are discerned: chr4 – B-X+, chr10 – B+X- and a hybrid type – B-X-: The “+, plus” means the sequence of the restriction site is correct: BinI: CCTAGG and XapI: AAATTCC. If a SNP is found there then the restriction site is disrupted “-, minus“. The DUCKS4 blast-workflow only distinguishes between chr4 and chr10 repeat units, we experienced so far that the hybrid repeat units are called as chr4 types with DUCKS4. The hybrid type is only relevant for determining the non-permissive 4qA subtype 4A166 as its proximal repeat units start with hybrid RU (D4Z4-order: hyb – hyb – mix hyb/c4) but also the permissive 4A166H should be verified as its proximal repeat units start with chr10 RU (D4Z4-order: c10 – c10 – mix c4/c10). Please refer to Giardina et al. 2024 (details in the Supplementary Infos), as well as Lemmers et al. 2010a and 2022a for further information to the various haplotypes and hybrid alleles.</a:t>
+            <a:t>The table is to be read from left to right: the first 6 columns (title DUCKS4) are the results from the DUCKS4 detailed output for the haplotypes and the composition of the repeat-sequence. The columns 7 to 9 (title Haplotype results) shows the resulting haplotype, permissive haplotypes are marked red. The columns 10-11 (title manual check) are displaying the data relevant for the manual check. Relevant is the SSLP repeat in CLUHP-4-201 gene (SSLP: chr4:193430066-193430226, T2T-chm13v2.0) and the first 3-5 repeat units with the restriction enzyme sites of the D4Z4-array for manual inspection within the alignment bam-files of the haplotypes from the DUCKS4-output. With the restriction enzyme sites (BinI (B)/XapI (X)) from Southern Blotting three types of RU are discerned: chr4 – B-X+, chr10 – B+X- and a hybrid type – B-X-: The “+, plus” means the sequence of the restriction site is correct: BinI: CCTAGG and XapI: AAATTCC. If a SNP is found there then the restriction site is disrupted “-, minus“. The DUCKS4 blast-workflow only distinguishes between chr4 and chr10 repeat units, we experienced so far that the hybrid repeat units are called as chr4 types with DUCKS4. The hybrid type is only relevant for determining the non-permissive 4qA subtype 4A166 as its proximal repeat units start with hybrid RU (D4Z4-order: hyb -</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="de-AT" sz="1100" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="de-AT" sz="1100"/>
+            <a:t>mix hyb/c4) but also the permissive 4A166H should be verified as its proximal repeat units start with chr10 RU (D4Z4-order: c10 – mix c4/c10/hyb). Please refer to Giardina et al. 2024 (details in the Supplementary Infos), as well as Lemmers et al. 2010a and 2022a for further information to the various haplotypes and hybrid alleles. </a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="de-AT" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr lang="de-AT" sz="1100"/>
+            <a:t>Update v1.1.0: Experimental automated BinI/XapI</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="de-AT" sz="1100" baseline="0"/>
+            <a:t> site detection added to ID2BAM2METH.</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="de-AT" sz="1100"/>
+          </a:br>
+          <a:endParaRPr lang="de-AT" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2810,22 +2836,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="158" t="s">
+      <c r="B1" s="191" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="191"/>
+      <c r="G1" s="191"/>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
@@ -2834,42 +2860,42 @@
     </row>
     <row r="19" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="159" t="s">
+      <c r="B20" s="192" t="s">
         <v>218</v>
       </c>
-      <c r="C20" s="160"/>
-      <c r="D20" s="160"/>
-      <c r="E20" s="160"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="160"/>
-      <c r="I20" s="160"/>
-      <c r="J20" s="160"/>
-      <c r="K20" s="160"/>
-      <c r="L20" s="160"/>
-      <c r="M20" s="160"/>
-      <c r="N20" s="161"/>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="193"/>
+      <c r="F20" s="193"/>
+      <c r="G20" s="193"/>
+      <c r="H20" s="193"/>
+      <c r="I20" s="193"/>
+      <c r="J20" s="193"/>
+      <c r="K20" s="193"/>
+      <c r="L20" s="193"/>
+      <c r="M20" s="193"/>
+      <c r="N20" s="194"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="183" t="s">
+      <c r="B21" s="171" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="184"/>
-      <c r="D21" s="184"/>
-      <c r="E21" s="184"/>
-      <c r="F21" s="184"/>
-      <c r="G21" s="184"/>
-      <c r="H21" s="174"/>
-      <c r="I21" s="185" t="s">
+      <c r="C21" s="172"/>
+      <c r="D21" s="172"/>
+      <c r="E21" s="172"/>
+      <c r="F21" s="172"/>
+      <c r="G21" s="172"/>
+      <c r="H21" s="173"/>
+      <c r="I21" s="174" t="s">
         <v>185</v>
       </c>
-      <c r="J21" s="184"/>
-      <c r="K21" s="174"/>
-      <c r="L21" s="186" t="s">
+      <c r="J21" s="172"/>
+      <c r="K21" s="173"/>
+      <c r="L21" s="175" t="s">
         <v>186</v>
       </c>
-      <c r="M21" s="174"/>
-      <c r="N21" s="187" t="s">
+      <c r="M21" s="173"/>
+      <c r="N21" s="176" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2889,10 +2915,10 @@
       <c r="F22" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="188" t="s">
+      <c r="G22" s="177" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="189"/>
+      <c r="H22" s="178"/>
       <c r="I22" s="40" t="s">
         <v>10</v>
       </c>
@@ -2908,22 +2934,22 @@
       <c r="M22" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="N22" s="163"/>
+      <c r="N22" s="170"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="190" t="s">
+      <c r="B23" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="192" t="s">
+      <c r="C23" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="194" t="s">
+      <c r="D23" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="175" t="s">
+      <c r="E23" s="167" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="162" t="s">
+      <c r="F23" s="168" t="s">
         <v>189</v>
       </c>
       <c r="G23" s="44" t="s">
@@ -2941,7 +2967,7 @@
       <c r="K23" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="L23" s="175" t="s">
+      <c r="L23" s="167" t="s">
         <v>21</v>
       </c>
       <c r="M23" s="48" t="s">
@@ -2952,11 +2978,11 @@
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="164"/>
-      <c r="C24" s="182"/>
-      <c r="D24" s="167"/>
-      <c r="E24" s="162"/>
-      <c r="F24" s="163"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="162"/>
+      <c r="D24" s="165"/>
+      <c r="E24" s="168"/>
+      <c r="F24" s="170"/>
       <c r="G24" s="50" t="s">
         <v>25</v>
       </c>
@@ -2972,7 +2998,7 @@
       <c r="K24" s="54" t="s">
         <v>193</v>
       </c>
-      <c r="L24" s="162"/>
+      <c r="L24" s="168"/>
       <c r="M24" s="55" t="s">
         <v>192</v>
       </c>
@@ -2981,29 +3007,29 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="164"/>
-      <c r="C25" s="182"/>
-      <c r="D25" s="167"/>
-      <c r="E25" s="162"/>
-      <c r="F25" s="177" t="s">
+      <c r="B25" s="159"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="165"/>
+      <c r="E25" s="168"/>
+      <c r="F25" s="179" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="180" t="s">
+      <c r="G25" s="182" t="s">
         <v>190</v>
       </c>
-      <c r="H25" s="180" t="s">
+      <c r="H25" s="182" t="s">
         <v>191</v>
       </c>
-      <c r="I25" s="178" t="s">
+      <c r="I25" s="180" t="s">
         <v>20</v>
       </c>
-      <c r="J25" s="167" t="s">
+      <c r="J25" s="165" t="s">
         <v>62</v>
       </c>
       <c r="K25" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="L25" s="176"/>
+      <c r="L25" s="169"/>
       <c r="M25" s="57" t="s">
         <v>195</v>
       </c>
@@ -3012,15 +3038,15 @@
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="164"/>
-      <c r="C26" s="182"/>
-      <c r="D26" s="167"/>
-      <c r="E26" s="162"/>
-      <c r="F26" s="178"/>
-      <c r="G26" s="181"/>
-      <c r="H26" s="181"/>
-      <c r="I26" s="179"/>
-      <c r="J26" s="163"/>
+      <c r="B26" s="159"/>
+      <c r="C26" s="162"/>
+      <c r="D26" s="165"/>
+      <c r="E26" s="168"/>
+      <c r="F26" s="180"/>
+      <c r="G26" s="183"/>
+      <c r="H26" s="183"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="170"/>
       <c r="K26" s="58" t="s">
         <v>78</v>
       </c>
@@ -3033,21 +3059,21 @@
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="164"/>
-      <c r="C27" s="182"/>
-      <c r="D27" s="167"/>
-      <c r="E27" s="162"/>
-      <c r="F27" s="178"/>
-      <c r="G27" s="168" t="s">
+      <c r="B27" s="159"/>
+      <c r="C27" s="162"/>
+      <c r="D27" s="165"/>
+      <c r="E27" s="168"/>
+      <c r="F27" s="180"/>
+      <c r="G27" s="184" t="s">
         <v>25</v>
       </c>
-      <c r="H27" s="172" t="s">
+      <c r="H27" s="185" t="s">
         <v>26</v>
       </c>
-      <c r="I27" s="162" t="s">
+      <c r="I27" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="J27" s="182" t="s">
+      <c r="J27" s="162" t="s">
         <v>28</v>
       </c>
       <c r="K27" s="60" t="s">
@@ -3062,15 +3088,15 @@
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="164"/>
-      <c r="C28" s="182"/>
-      <c r="D28" s="195"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="179"/>
-      <c r="G28" s="163"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="163"/>
-      <c r="J28" s="163"/>
+      <c r="B28" s="159"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="169"/>
+      <c r="F28" s="181"/>
+      <c r="G28" s="170"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="170"/>
+      <c r="J28" s="170"/>
       <c r="K28" s="61" t="s">
         <v>33</v>
       </c>
@@ -3083,25 +3109,25 @@
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="164"/>
-      <c r="C29" s="182"/>
-      <c r="D29" s="169" t="s">
+      <c r="B29" s="159"/>
+      <c r="C29" s="162"/>
+      <c r="D29" s="187" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="162"/>
-      <c r="F29" s="162" t="s">
+      <c r="E29" s="168"/>
+      <c r="F29" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="G29" s="168" t="s">
+      <c r="G29" s="184" t="s">
         <v>196</v>
       </c>
-      <c r="H29" s="172" t="s">
+      <c r="H29" s="185" t="s">
         <v>191</v>
       </c>
-      <c r="I29" s="162" t="s">
+      <c r="I29" s="168" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="165" t="s">
+      <c r="J29" s="195" t="s">
         <v>63</v>
       </c>
       <c r="K29" s="60" t="s">
@@ -3116,15 +3142,15 @@
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="164"/>
-      <c r="C30" s="182"/>
-      <c r="D30" s="170"/>
-      <c r="E30" s="166"/>
-      <c r="F30" s="166"/>
-      <c r="G30" s="166"/>
-      <c r="H30" s="173"/>
-      <c r="I30" s="166"/>
-      <c r="J30" s="166"/>
+      <c r="B30" s="159"/>
+      <c r="C30" s="162"/>
+      <c r="D30" s="188"/>
+      <c r="E30" s="186"/>
+      <c r="F30" s="186"/>
+      <c r="G30" s="186"/>
+      <c r="H30" s="190"/>
+      <c r="I30" s="186"/>
+      <c r="J30" s="186"/>
       <c r="K30" s="60" t="s">
         <v>198</v>
       </c>
@@ -3137,15 +3163,15 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="164"/>
-      <c r="C31" s="182"/>
-      <c r="D31" s="170"/>
-      <c r="E31" s="166"/>
-      <c r="F31" s="166"/>
-      <c r="G31" s="166"/>
-      <c r="H31" s="173"/>
-      <c r="I31" s="166"/>
-      <c r="J31" s="166"/>
+      <c r="B31" s="159"/>
+      <c r="C31" s="162"/>
+      <c r="D31" s="188"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="186"/>
+      <c r="G31" s="186"/>
+      <c r="H31" s="190"/>
+      <c r="I31" s="186"/>
+      <c r="J31" s="186"/>
       <c r="K31" s="60" t="s">
         <v>38</v>
       </c>
@@ -3158,15 +3184,15 @@
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="164"/>
-      <c r="C32" s="193"/>
-      <c r="D32" s="171"/>
-      <c r="E32" s="163"/>
-      <c r="F32" s="163"/>
-      <c r="G32" s="163"/>
-      <c r="H32" s="174"/>
-      <c r="I32" s="163"/>
-      <c r="J32" s="163"/>
+      <c r="B32" s="159"/>
+      <c r="C32" s="163"/>
+      <c r="D32" s="189"/>
+      <c r="E32" s="170"/>
+      <c r="F32" s="170"/>
+      <c r="G32" s="170"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="170"/>
+      <c r="J32" s="170"/>
       <c r="K32" s="61" t="s">
         <v>40</v>
       </c>
@@ -3179,7 +3205,7 @@
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B33" s="191"/>
+      <c r="B33" s="160"/>
       <c r="C33" s="62" t="s">
         <v>42</v>
       </c>
@@ -3214,31 +3240,31 @@
       </c>
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="164" t="s">
+      <c r="B34" s="159" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="167" t="s">
+      <c r="C34" s="165" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="167" t="s">
+      <c r="D34" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="E34" s="162" t="s">
+      <c r="E34" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="F34" s="162" t="s">
+      <c r="F34" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="G34" s="168" t="s">
+      <c r="G34" s="184" t="s">
         <v>196</v>
       </c>
-      <c r="H34" s="168" t="s">
+      <c r="H34" s="184" t="s">
         <v>191</v>
       </c>
-      <c r="I34" s="162" t="s">
+      <c r="I34" s="168" t="s">
         <v>20</v>
       </c>
-      <c r="J34" s="167" t="s">
+      <c r="J34" s="165" t="s">
         <v>62</v>
       </c>
       <c r="K34" s="67" t="s">
@@ -3253,19 +3279,19 @@
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B35" s="166"/>
-      <c r="C35" s="166"/>
-      <c r="D35" s="166"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="166"/>
-      <c r="G35" s="166"/>
-      <c r="H35" s="166"/>
-      <c r="I35" s="166"/>
-      <c r="J35" s="166"/>
+      <c r="B35" s="186"/>
+      <c r="C35" s="186"/>
+      <c r="D35" s="186"/>
+      <c r="E35" s="186"/>
+      <c r="F35" s="186"/>
+      <c r="G35" s="186"/>
+      <c r="H35" s="186"/>
+      <c r="I35" s="186"/>
+      <c r="J35" s="186"/>
       <c r="K35" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="L35" s="162" t="s">
+      <c r="L35" s="168" t="s">
         <v>44</v>
       </c>
       <c r="M35" s="48"/>
@@ -3274,38 +3300,38 @@
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="163"/>
-      <c r="C36" s="163"/>
-      <c r="D36" s="163"/>
+      <c r="B36" s="170"/>
+      <c r="C36" s="170"/>
+      <c r="D36" s="170"/>
       <c r="E36" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="163"/>
-      <c r="G36" s="163"/>
-      <c r="H36" s="163"/>
-      <c r="I36" s="163"/>
-      <c r="J36" s="163"/>
+      <c r="F36" s="170"/>
+      <c r="G36" s="170"/>
+      <c r="H36" s="170"/>
+      <c r="I36" s="170"/>
+      <c r="J36" s="170"/>
       <c r="K36" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="L36" s="163"/>
+      <c r="L36" s="170"/>
       <c r="M36" s="48"/>
       <c r="N36" s="49" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="164" t="s">
+      <c r="B37" s="159" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="165" t="s">
+      <c r="C37" s="195" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="165" t="s">
+      <c r="D37" s="195" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="162"/>
-      <c r="F37" s="162" t="s">
+      <c r="E37" s="168"/>
+      <c r="F37" s="168" t="s">
         <v>36</v>
       </c>
       <c r="G37" s="65" t="s">
@@ -3332,11 +3358,11 @@
       </c>
     </row>
     <row r="38" spans="2:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="B38" s="163"/>
-      <c r="C38" s="163"/>
-      <c r="D38" s="163"/>
-      <c r="E38" s="163"/>
-      <c r="F38" s="163"/>
+      <c r="B38" s="170"/>
+      <c r="C38" s="170"/>
+      <c r="D38" s="170"/>
+      <c r="E38" s="170"/>
+      <c r="F38" s="170"/>
       <c r="G38" s="65" t="s">
         <v>25</v>
       </c>
@@ -3402,34 +3428,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="B23:B33"/>
-    <mergeCell ref="C23:C32"/>
-    <mergeCell ref="D23:D28"/>
-    <mergeCell ref="E23:E28"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="L23:L25"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="I34:I36"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="E29:E32"/>
-    <mergeCell ref="F29:F32"/>
-    <mergeCell ref="G29:G32"/>
-    <mergeCell ref="H29:H32"/>
-    <mergeCell ref="I29:I32"/>
     <mergeCell ref="B1:G2"/>
     <mergeCell ref="B20:N20"/>
     <mergeCell ref="L35:L36"/>
@@ -3446,6 +3444,34 @@
     <mergeCell ref="F34:F36"/>
     <mergeCell ref="G34:G36"/>
     <mergeCell ref="H34:H36"/>
+    <mergeCell ref="I34:I36"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="E29:E32"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="H29:H32"/>
+    <mergeCell ref="I29:I32"/>
+    <mergeCell ref="L23:L25"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B23:B33"/>
+    <mergeCell ref="C23:C32"/>
+    <mergeCell ref="D23:D28"/>
+    <mergeCell ref="E23:E28"/>
+    <mergeCell ref="F23:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3542,40 +3568,40 @@
       <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="202" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="211"/>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="212"/>
-      <c r="S4" s="213" t="s">
+      <c r="C4" s="203"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="203"/>
+      <c r="H4" s="203"/>
+      <c r="I4" s="203"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="203"/>
+      <c r="L4" s="203"/>
+      <c r="M4" s="203"/>
+      <c r="N4" s="203"/>
+      <c r="O4" s="203"/>
+      <c r="P4" s="203"/>
+      <c r="Q4" s="203"/>
+      <c r="R4" s="204"/>
+      <c r="S4" s="205" t="s">
         <v>13</v>
       </c>
-      <c r="T4" s="214" t="s">
+      <c r="T4" s="207" t="s">
         <v>83</v>
       </c>
-      <c r="U4" s="211"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="211"/>
-      <c r="Y4" s="212"/>
-      <c r="Z4" s="215" t="s">
+      <c r="U4" s="203"/>
+      <c r="V4" s="203"/>
+      <c r="W4" s="203"/>
+      <c r="X4" s="203"/>
+      <c r="Y4" s="204"/>
+      <c r="Z4" s="208" t="s">
         <v>84</v>
       </c>
-      <c r="AA4" s="216" t="s">
+      <c r="AA4" s="196" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3583,105 +3609,105 @@
       <c r="B5" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="218">
+      <c r="C5" s="198">
         <v>27</v>
       </c>
-      <c r="D5" s="204">
+      <c r="D5" s="200">
         <v>75</v>
       </c>
-      <c r="E5" s="204">
+      <c r="E5" s="200">
         <v>165</v>
       </c>
-      <c r="F5" s="204">
+      <c r="F5" s="200">
         <v>185</v>
       </c>
-      <c r="G5" s="204">
+      <c r="G5" s="200">
         <v>196</v>
       </c>
-      <c r="H5" s="204">
+      <c r="H5" s="200">
         <v>200</v>
       </c>
-      <c r="I5" s="204">
+      <c r="I5" s="200">
         <v>242</v>
       </c>
-      <c r="J5" s="204">
+      <c r="J5" s="200">
         <v>258</v>
       </c>
-      <c r="K5" s="204">
+      <c r="K5" s="200">
         <v>309</v>
       </c>
-      <c r="L5" s="204">
+      <c r="L5" s="200">
         <v>332</v>
       </c>
-      <c r="M5" s="204">
+      <c r="M5" s="200">
         <v>340</v>
       </c>
-      <c r="N5" s="204">
+      <c r="N5" s="200">
         <v>383</v>
       </c>
-      <c r="O5" s="204">
+      <c r="O5" s="200">
         <v>420</v>
       </c>
-      <c r="P5" s="204">
+      <c r="P5" s="200">
         <v>427</v>
       </c>
-      <c r="Q5" s="204">
+      <c r="Q5" s="200">
         <v>456</v>
       </c>
-      <c r="R5" s="206">
+      <c r="R5" s="215">
         <v>462</v>
       </c>
-      <c r="S5" s="209"/>
-      <c r="T5" s="208" t="s">
+      <c r="S5" s="206"/>
+      <c r="T5" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="U5" s="199" t="s">
+      <c r="U5" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="V5" s="199" t="s">
+      <c r="V5" s="218" t="s">
         <v>87</v>
       </c>
-      <c r="W5" s="199" t="s">
+      <c r="W5" s="218" t="s">
         <v>88</v>
       </c>
-      <c r="X5" s="201" t="s">
+      <c r="X5" s="210" t="s">
         <v>89</v>
       </c>
-      <c r="Y5" s="203" t="s">
+      <c r="Y5" s="211" t="s">
         <v>90</v>
       </c>
-      <c r="Z5" s="202"/>
-      <c r="AA5" s="217"/>
+      <c r="Z5" s="209"/>
+      <c r="AA5" s="197"/>
     </row>
     <row r="6" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="219"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="205"/>
-      <c r="G6" s="205"/>
-      <c r="H6" s="205"/>
-      <c r="I6" s="205"/>
-      <c r="J6" s="205"/>
-      <c r="K6" s="205"/>
-      <c r="L6" s="205"/>
-      <c r="M6" s="205"/>
-      <c r="N6" s="205"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="205"/>
-      <c r="Q6" s="205"/>
-      <c r="R6" s="207"/>
-      <c r="S6" s="209"/>
-      <c r="T6" s="209"/>
-      <c r="U6" s="200"/>
-      <c r="V6" s="200"/>
-      <c r="W6" s="200"/>
-      <c r="X6" s="202"/>
-      <c r="Y6" s="197"/>
-      <c r="Z6" s="202"/>
-      <c r="AA6" s="217"/>
+      <c r="C6" s="199"/>
+      <c r="D6" s="201"/>
+      <c r="E6" s="201"/>
+      <c r="F6" s="201"/>
+      <c r="G6" s="201"/>
+      <c r="H6" s="201"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="201"/>
+      <c r="K6" s="201"/>
+      <c r="L6" s="201"/>
+      <c r="M6" s="201"/>
+      <c r="N6" s="201"/>
+      <c r="O6" s="201"/>
+      <c r="P6" s="201"/>
+      <c r="Q6" s="201"/>
+      <c r="R6" s="216"/>
+      <c r="S6" s="206"/>
+      <c r="T6" s="206"/>
+      <c r="U6" s="219"/>
+      <c r="V6" s="219"/>
+      <c r="W6" s="219"/>
+      <c r="X6" s="209"/>
+      <c r="Y6" s="212"/>
+      <c r="Z6" s="209"/>
+      <c r="AA6" s="197"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="82" t="s">
@@ -3738,7 +3764,7 @@
       <c r="S7" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="T7" s="196" t="s">
+      <c r="T7" s="213" t="s">
         <v>28</v>
       </c>
       <c r="U7" s="85" t="s">
@@ -3816,7 +3842,7 @@
       <c r="S8" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="T8" s="197"/>
+      <c r="T8" s="212"/>
       <c r="U8" s="91" t="s">
         <v>28</v>
       </c>
@@ -3892,7 +3918,7 @@
       <c r="S9" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="T9" s="197"/>
+      <c r="T9" s="212"/>
       <c r="U9" s="91" t="s">
         <v>28</v>
       </c>
@@ -3968,7 +3994,7 @@
       <c r="S10" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="T10" s="197"/>
+      <c r="T10" s="212"/>
       <c r="U10" s="91" t="s">
         <v>28</v>
       </c>
@@ -4044,7 +4070,7 @@
       <c r="S11" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="T11" s="197"/>
+      <c r="T11" s="212"/>
       <c r="U11" s="91" t="s">
         <v>62</v>
       </c>
@@ -4122,7 +4148,7 @@
       <c r="S12" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="T12" s="197"/>
+      <c r="T12" s="212"/>
       <c r="U12" s="91" t="s">
         <v>62</v>
       </c>
@@ -4200,7 +4226,7 @@
       <c r="S13" s="98" t="s">
         <v>99</v>
       </c>
-      <c r="T13" s="197"/>
+      <c r="T13" s="212"/>
       <c r="U13" s="91" t="s">
         <v>62</v>
       </c>
@@ -4278,7 +4304,7 @@
       <c r="S14" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="T14" s="197"/>
+      <c r="T14" s="212"/>
       <c r="U14" s="91" t="s">
         <v>63</v>
       </c>
@@ -4354,7 +4380,7 @@
       <c r="S15" s="105" t="s">
         <v>114</v>
       </c>
-      <c r="T15" s="197"/>
+      <c r="T15" s="212"/>
       <c r="U15" s="104" t="s">
         <v>63</v>
       </c>
@@ -4430,7 +4456,7 @@
       <c r="S16" s="108" t="s">
         <v>99</v>
       </c>
-      <c r="T16" s="197"/>
+      <c r="T16" s="212"/>
       <c r="U16" s="109" t="s">
         <v>28</v>
       </c>
@@ -4506,7 +4532,7 @@
       <c r="S17" s="108" t="s">
         <v>99</v>
       </c>
-      <c r="T17" s="197"/>
+      <c r="T17" s="212"/>
       <c r="U17" s="79" t="s">
         <v>28</v>
       </c>
@@ -4582,7 +4608,7 @@
       <c r="S18" s="115" t="s">
         <v>99</v>
       </c>
-      <c r="T18" s="197"/>
+      <c r="T18" s="212"/>
       <c r="U18" s="103" t="s">
         <v>62</v>
       </c>
@@ -4660,7 +4686,7 @@
       <c r="S19" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="T19" s="197"/>
+      <c r="T19" s="212"/>
       <c r="U19" s="109" t="s">
         <v>28</v>
       </c>
@@ -4736,7 +4762,7 @@
       <c r="S20" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="T20" s="197"/>
+      <c r="T20" s="212"/>
       <c r="U20" s="79" t="s">
         <v>28</v>
       </c>
@@ -4812,7 +4838,7 @@
       <c r="S21" s="124" t="s">
         <v>99</v>
       </c>
-      <c r="T21" s="197"/>
+      <c r="T21" s="212"/>
       <c r="U21" s="103" t="s">
         <v>28</v>
       </c>
@@ -4888,7 +4914,7 @@
       <c r="S22" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="T22" s="197"/>
+      <c r="T22" s="212"/>
       <c r="U22" s="109" t="s">
         <v>62</v>
       </c>
@@ -4966,7 +4992,7 @@
       <c r="S23" s="128" t="s">
         <v>112</v>
       </c>
-      <c r="T23" s="197"/>
+      <c r="T23" s="212"/>
       <c r="U23" s="79" t="s">
         <v>62</v>
       </c>
@@ -5044,7 +5070,7 @@
       <c r="S24" s="131" t="s">
         <v>114</v>
       </c>
-      <c r="T24" s="197"/>
+      <c r="T24" s="212"/>
       <c r="U24" s="79" t="s">
         <v>62</v>
       </c>
@@ -5122,7 +5148,7 @@
       <c r="S25" s="131" t="s">
         <v>114</v>
       </c>
-      <c r="T25" s="197"/>
+      <c r="T25" s="212"/>
       <c r="U25" s="79" t="s">
         <v>62</v>
       </c>
@@ -5200,7 +5226,7 @@
       <c r="S26" s="128" t="s">
         <v>116</v>
       </c>
-      <c r="T26" s="197"/>
+      <c r="T26" s="212"/>
       <c r="U26" s="79" t="s">
         <v>63</v>
       </c>
@@ -5276,7 +5302,7 @@
       <c r="S27" s="128" t="s">
         <v>117</v>
       </c>
-      <c r="T27" s="197"/>
+      <c r="T27" s="212"/>
       <c r="U27" s="79" t="s">
         <v>63</v>
       </c>
@@ -5352,7 +5378,7 @@
       <c r="S28" s="132" t="s">
         <v>114</v>
       </c>
-      <c r="T28" s="197"/>
+      <c r="T28" s="212"/>
       <c r="U28" s="79" t="s">
         <v>63</v>
       </c>
@@ -5428,7 +5454,7 @@
       <c r="S29" s="137" t="s">
         <v>120</v>
       </c>
-      <c r="T29" s="198"/>
+      <c r="T29" s="214"/>
       <c r="U29" s="135" t="s">
         <v>63</v>
       </c>
@@ -5504,7 +5530,7 @@
       <c r="S30" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="T30" s="196" t="s">
+      <c r="T30" s="213" t="s">
         <v>62</v>
       </c>
       <c r="U30" s="84" t="s">
@@ -5584,7 +5610,7 @@
       <c r="S31" s="149" t="s">
         <v>44</v>
       </c>
-      <c r="T31" s="197"/>
+      <c r="T31" s="212"/>
       <c r="U31" s="79" t="s">
         <v>62</v>
       </c>
@@ -5662,7 +5688,7 @@
       <c r="S32" s="149" t="s">
         <v>44</v>
       </c>
-      <c r="T32" s="197"/>
+      <c r="T32" s="212"/>
       <c r="U32" s="79" t="s">
         <v>62</v>
       </c>
@@ -5740,7 +5766,7 @@
       <c r="S33" s="152" t="s">
         <v>44</v>
       </c>
-      <c r="T33" s="198"/>
+      <c r="T33" s="214"/>
       <c r="U33" s="135" t="s">
         <v>63</v>
       </c>
@@ -5816,7 +5842,7 @@
       <c r="S34" s="144" t="s">
         <v>54</v>
       </c>
-      <c r="T34" s="196" t="s">
+      <c r="T34" s="213" t="s">
         <v>63</v>
       </c>
       <c r="U34" s="84" t="s">
@@ -5894,7 +5920,7 @@
       <c r="S35" s="154" t="s">
         <v>44</v>
       </c>
-      <c r="T35" s="197"/>
+      <c r="T35" s="212"/>
       <c r="U35" s="79" t="s">
         <v>63</v>
       </c>
@@ -5970,7 +5996,7 @@
       <c r="S36" s="155" t="s">
         <v>123</v>
       </c>
-      <c r="T36" s="198"/>
+      <c r="T36" s="214"/>
       <c r="U36" s="135" t="s">
         <v>63</v>
       </c>
@@ -10811,6 +10837,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="T30:T33"/>
+    <mergeCell ref="T34:T36"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="T7:T29"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="T5:T6"/>
     <mergeCell ref="AA4:AA6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
@@ -10827,20 +10867,6 @@
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="T7:T29"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="T30:T33"/>
-    <mergeCell ref="T34:T36"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="W5:W6"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
